--- a/Assets/StreamingAssets/Excel/DeepExploreDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DeepExploreDropListConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C69B06A-BE40-4C2B-9852-248EF0364EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327D18AA-F600-4543-A035-207AA87E6045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7692" yWindow="108" windowWidth="13968" windowHeight="12204" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoralCoast" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
   <si>
     <t>CardId</t>
   </si>
@@ -120,6 +120,22 @@
   </si>
   <si>
     <t>水壶兰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四角菱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食果鲀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裙水母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狮子水母</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -449,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
@@ -788,6 +804,111 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1500</v>
+      </c>
+      <c r="D10">
+        <v>5000</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>-1000</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>4000</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>-1000</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1500</v>
+      </c>
+      <c r="D12">
+        <v>3000</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>-1000</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -797,7 +918,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -1169,6 +1290,76 @@
         <v>0</v>
       </c>
       <c r="P10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>2000</v>
+      </c>
+      <c r="D11">
+        <v>6000</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>-1000</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1000</v>
+      </c>
+      <c r="D12">
+        <v>3000</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>-1000</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Excel/DeepExploreDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DeepExploreDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327D18AA-F600-4543-A035-207AA87E6045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868C7EC0-845A-40E2-B841-C7B2335E3311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7692" yWindow="108" windowWidth="13968" windowHeight="12204" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoralCoast" sheetId="1" r:id="rId1"/>
@@ -127,15 +127,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>食果鲀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>裙水母</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>狮子水母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食果豚</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -466,18 +466,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" customWidth="1"/>
-    <col min="4" max="4" width="7.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.4140625" customWidth="1"/>
+    <col min="3" max="3" width="5.08203125" customWidth="1"/>
+    <col min="4" max="4" width="7.4140625" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="6" max="6" width="19.08203125" customWidth="1"/>
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -527,7 +527,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -559,7 +559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -594,7 +594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -629,7 +629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -664,7 +664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
@@ -839,9 +839,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -874,9 +874,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -912,26 +912,26 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" customWidth="1"/>
-    <col min="4" max="4" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.4140625" customWidth="1"/>
+    <col min="3" max="3" width="5.08203125" customWidth="1"/>
+    <col min="4" max="4" width="7.4140625" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="6" max="6" width="19.08203125" customWidth="1"/>
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="13.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -981,7 +981,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -1293,9 +1293,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1328,9 +1328,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -1373,18 +1373,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.44140625" customWidth="1"/>
-    <col min="4" max="4" width="7.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.4140625" customWidth="1"/>
+    <col min="3" max="3" width="5.4140625" customWidth="1"/>
+    <col min="4" max="4" width="7.4140625" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="6" max="6" width="19.08203125" customWidth="1"/>
     <col min="7" max="7" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>

--- a/Assets/StreamingAssets/Excel/DeepExploreDropListConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/DeepExploreDropListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\22575\Documents\GitHub\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868C7EC0-845A-40E2-B841-C7B2335E3311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B537BC-5592-49FF-B251-825917A0C925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoralCoast" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,11 @@
     <sheet name="SpaceshipOuterHull" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="35">
   <si>
     <t>CardId</t>
   </si>
@@ -465,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
@@ -906,6 +901,41 @@
         <v>0</v>
       </c>
       <c r="P12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2000</v>
+      </c>
+      <c r="D13">
+        <v>4000</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>-1000</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="b">
         <v>0</v>
       </c>
     </row>
